--- a/data/trans_orig/IP19C05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81724</t>
+          <t>81306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>76588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160154</t>
+          <t>160038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
+          <t>95952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100172</t>
+          <t>100107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199231</t>
+          <t>198911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204267</t>
+          <t>204271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157688</t>
+          <t>157846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162897</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169264</t>
+          <t>169096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329185</t>
+          <t>329342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335958</t>
+          <t>335928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,47 +2119,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7925</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>343090</t>
+          <t>343477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>349664</t>
+          <t>349693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,49 +2232,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>353223</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>360432</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>353806</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>360414</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1057</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700022</t>
+          <t>700021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708970</t>
+          <t>709156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75046</t>
+          <t>75050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88080</t>
+          <t>88815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165983</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>116101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>123114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126341</t>
+          <t>126274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131441</t>
+          <t>131438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245287</t>
+          <t>245437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254183</t>
+          <t>254141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138463</t>
+          <t>139250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146399</t>
+          <t>146401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133321</t>
+          <t>133569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139894</t>
+          <t>139888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276085</t>
+          <t>276020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284817</t>
+          <t>284952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>338781</t>
+          <t>338143</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348967</t>
+          <t>348732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>354820</t>
+          <t>354383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>363162</t>
+          <t>363154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>696723</t>
+          <t>697157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>710096</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>142232</t>
+          <t>142095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148202</t>
+          <t>148186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144434</t>
+          <t>144671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289689</t>
+          <t>289545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296646</t>
+          <t>296374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17736</t>
+          <t>17865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133694</t>
+          <t>132492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142036</t>
+          <t>141915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125751</t>
+          <t>125459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133565</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262624</t>
+          <t>262495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273800</t>
+          <t>273927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347580</t>
+          <t>346373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>357703</t>
+          <t>357356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356614</t>
+          <t>356304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365080</t>
+          <t>365149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707587</t>
+          <t>707595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>720602</t>
+          <t>721589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3830</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4605</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4715</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79733</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76978</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>83693</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>81306</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>81078</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79733</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>76588</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>248</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>160038</t>
+          <t>160148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3241</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5612</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>104158</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>99415</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>98551</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>95952</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>95986</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>104158</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>100107</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>303</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198911</t>
+          <t>197911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204271</t>
+          <t>204273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2103</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5651</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6462</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1286</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172415</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>169189</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>161394</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>157846</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>162899</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>157035</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>162898</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172415</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>169096</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>497</t>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335928</t>
+          <t>335962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,59 +2099,59 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>3387</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7453</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7349</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8508</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2207,67 +2207,67 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>358199</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>353796</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>360400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>347543</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>343477</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>349693</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>343581</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>349675</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>358199</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>353223</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>360432</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700021</t>
+          <t>700248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>709156</t>
+          <t>709234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,102 +3017,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3609</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3249</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91344</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88455</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>77245</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>75050</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>74974</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>91344</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88815</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>232</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165202</t>
+          <t>165729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5512</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4536</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8985</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9319</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130002</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126574</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>120550</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>116101</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>123114</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>115767</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123506</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130002</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>126274</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131438</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245437</t>
+          <t>244917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254141</t>
+          <t>253826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3414</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8154</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4307</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8670</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8495</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7614</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137769</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>133029</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>139902</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>143613</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>139250</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146401</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>139425</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>146458</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>137769</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>133569</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>139888</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>276020</t>
+          <t>276059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284952</t>
+          <t>285286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141183</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11351</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9286</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15848</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15840</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11619</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>359784</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>354651</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>363202</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>491</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>344705</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>338143</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>348732</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>338151</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>348662</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>359784</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>354383</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>363154</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>697157</t>
+          <t>697090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>710277</t>
+          <t>709793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,92 +5302,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2770</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6822</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6671</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>1330</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4670</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148011</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145358</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>146147</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>142095</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148186</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>142246</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148187</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148011</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144671</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>415</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289545</t>
+          <t>289813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>296374</t>
+          <t>296928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10093</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6334</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12613</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11908</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4823</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9796</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>130432</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>125162</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133566</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>138771</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>132492</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>141915</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>133197</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>142407</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>130432</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>125459</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>133578</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262495</t>
+          <t>262412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273927</t>
+          <t>273919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>135255</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>135255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11413</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9104</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5262</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16245</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5089</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15050</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11704</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>361855</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>356595</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>365568</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>514</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>353514</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>346373</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>357356</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>347568</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>357529</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>361855</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>356304</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>365149</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707595</t>
+          <t>707825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>721589</t>
+          <t>720767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368008</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
